--- a/beam_structure.xlsx
+++ b/beam_structure.xlsx
@@ -719,7 +719,7 @@
         <v>0.5457681227392567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8905813499290538</v>
+        <v>0.8905813499290539</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>0.28</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5386876470026674</v>
+        <v>0.5386876470026672</v>
       </c>
       <c r="K4" t="n">
         <v>0.6658545503552404</v>
@@ -748,7 +748,7 @@
         <v>1.410302569216248</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7774375248306198</v>
+        <v>-0.7774375248306199</v>
       </c>
       <c r="N4" t="n">
         <v>0.6289601696333715</v>
@@ -760,7 +760,7 @@
         <v>-0.5375903897991704</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.664498265862875</v>
+        <v>-0.6644982658628751</v>
       </c>
       <c r="R4" t="n">
         <v>0.5190747802203532</v>
@@ -1031,7 +1031,7 @@
         <v>0.7524369560488918</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2997085997685378</v>
+        <v>0.299708599768538</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1054,13 +1054,13 @@
         <v>1.077375294043014</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3329272751789755</v>
+        <v>0.3329272751789757</v>
       </c>
       <c r="L8" t="n">
         <v>1.204542197362812</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2952418088443086</v>
+        <v>-0.2952418088443087</v>
       </c>
       <c r="N8" t="n">
         <v>0.9554225632202438</v>
@@ -1072,16 +1072,16 @@
         <v>-0.6974829052795896</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2155340710173908</v>
+        <v>-0.2155340710173909</v>
       </c>
       <c r="R8" t="n">
-        <v>0.683419827831629</v>
+        <v>0.6834198278316291</v>
       </c>
       <c r="S8" t="n">
         <v>0.6529547236624327</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2017741061690761</v>
+        <v>0.2017741061690762</v>
       </c>
       <c r="U8" t="n">
         <v>0.73002557415928</v>
@@ -1343,7 +1343,7 @@
         <v>0.8593172624177625</v>
       </c>
       <c r="D12" t="n">
-        <v>1.30113532876273</v>
+        <v>1.301135328762731</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>0.28</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3329272751789759</v>
+        <v>0.3329272751789755</v>
       </c>
       <c r="K12" t="n">
         <v>1.204542197362812</v>
@@ -1372,28 +1372,28 @@
         <v>1.077375294043014</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9638612634666792</v>
+        <v>-0.9638612634666793</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2664047011379806</v>
+        <v>0.2664047011379804</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1739502080139231</v>
+        <v>-0.173950208013923</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.6293577649358088</v>
+        <v>-0.6293577649358089</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7573969427235075</v>
+        <v>0.7573969427235077</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2017741061690763</v>
+        <v>0.2017741061690761</v>
       </c>
       <c r="T12" t="n">
-        <v>0.73002557415928</v>
+        <v>0.7300255741592802</v>
       </c>
       <c r="U12" t="n">
         <v>0.6529547236624327</v>
@@ -1441,7 +1441,7 @@
         <v>0.28</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3329272751789754</v>
+        <v>-0.3329272751789757</v>
       </c>
       <c r="K13" t="n">
         <v>1.204542197362812</v>
@@ -1450,16 +1450,16 @@
         <v>1.077375294043014</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9638612634666793</v>
+        <v>-0.9638612634666792</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2664047011379803</v>
+        <v>-0.2664047011379805</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1739502080139229</v>
+        <v>0.1739502080139231</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.6293577649358089</v>
@@ -1468,10 +1468,10 @@
         <v>0.7573969427235075</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.201774106169076</v>
+        <v>-0.2017741061690762</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7300255741592802</v>
+        <v>0.73002557415928</v>
       </c>
       <c r="U13" t="n">
         <v>0.6529547236624327</v>
@@ -1655,7 +1655,7 @@
         <v>1.155404777809637</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3648638281031875</v>
+        <v>0.3648638281031877</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1678,13 +1678,13 @@
         <v>1.410302569216248</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5386876470026671</v>
+        <v>0.5386876470026675</v>
       </c>
       <c r="L16" t="n">
         <v>0.6658545503552405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.356822089763472</v>
+        <v>-0.3568220897634722</v>
       </c>
       <c r="N16" t="n">
         <v>0.9341723589663894</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3769835854750665</v>
+        <v>-0.3769835854750664</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1439949164462267</v>
@@ -1705,7 +1705,7 @@
         <v>0.8547288298280291</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3264773618197983</v>
+        <v>0.3264773618197985</v>
       </c>
       <c r="U16" t="n">
         <v>0.4035482123365094</v>
@@ -1714,7 +1714,7 @@
         <v>-0.01424548049713392</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="X16" t="n">
         <v>-0.006725803538941921</v>
@@ -2435,7 +2435,7 @@
         <v>1.367627380743659</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7297276562338513</v>
+        <v>0.7297276562338512</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>0.3329272751789757</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6666666666717984</v>
+        <v>-0.6666666666717983</v>
       </c>
       <c r="N26" t="n">
         <v>0.74535599249534</v>
@@ -2476,7 +2476,7 @@
         <v>-0.1503935391635119</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1345160707804196</v>
+        <v>-0.1345160707804195</v>
       </c>
       <c r="R26" t="n">
         <v>0.9794320854861098</v>
@@ -2485,7 +2485,7 @@
         <v>0.73002557415928</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6529547236624328</v>
+        <v>0.6529547236624327</v>
       </c>
       <c r="U26" t="n">
         <v>0.2017741061690762</v>
@@ -2494,7 +2494,7 @@
         <v>-0.0121670929026545</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.01088257872770715</v>
+        <v>-0.01088257872770693</v>
       </c>
       <c r="X26" t="n">
         <v>-0.003362901769484505</v>
@@ -2689,43 +2689,43 @@
         <v>0.28</v>
       </c>
       <c r="J29" t="n">
-        <v>1.204542197362811</v>
+        <v>1.204542197362812</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.077375294043015</v>
+        <v>-1.077375294043014</v>
       </c>
       <c r="L29" t="n">
         <v>0.3329272751789757</v>
       </c>
       <c r="M29" t="n">
-        <v>0.666666666671799</v>
+        <v>0.6666666666717982</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7453559924953396</v>
+        <v>0.7453559924953401</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.1503935391635118</v>
+        <v>-0.1503935391635119</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1345160707804197</v>
+        <v>0.1345160707804195</v>
       </c>
       <c r="R29" t="n">
         <v>0.9794320854861098</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7300255741592796</v>
+        <v>0.7300255741592802</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.6529547236624332</v>
+        <v>-0.6529547236624326</v>
       </c>
       <c r="U29" t="n">
         <v>0.2017741061690762</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.01216709290265494</v>
+        <v>-0.01216709290265472</v>
       </c>
       <c r="W29" t="n">
         <v>0.01088257872770737</v>
@@ -3059,7 +3059,7 @@
         <v>1.773965272846134</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7297276562338513</v>
+        <v>0.7297276562338512</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>-0.3329272751789759</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6666666666717984</v>
+        <v>-0.6666666666717983</v>
       </c>
       <c r="N34" t="n">
         <v>0.74535599249534</v>
@@ -3109,7 +3109,7 @@
         <v>0.73002557415928</v>
       </c>
       <c r="T34" t="n">
-        <v>0.6529547236624328</v>
+        <v>0.6529547236624327</v>
       </c>
       <c r="U34" t="n">
         <v>-0.2017741061690763</v>
@@ -3118,7 +3118,7 @@
         <v>-0.0121670929026545</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.01088257872770715</v>
+        <v>-0.01088257872770693</v>
       </c>
       <c r="X34" t="n">
         <v>0.003362901769484561</v>
@@ -3313,43 +3313,43 @@
         <v>0.28</v>
       </c>
       <c r="J37" t="n">
-        <v>1.204542197362811</v>
+        <v>1.204542197362812</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.077375294043015</v>
+        <v>-1.077375294043014</v>
       </c>
       <c r="L37" t="n">
         <v>-0.3329272751789759</v>
       </c>
       <c r="M37" t="n">
-        <v>0.666666666671799</v>
+        <v>0.6666666666717982</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7453559924953396</v>
+        <v>0.7453559924953401</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1503935391635118</v>
+        <v>0.150393539163512</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.1345160707804197</v>
+        <v>-0.1345160707804196</v>
       </c>
       <c r="R37" t="n">
         <v>0.9794320854861098</v>
       </c>
       <c r="S37" t="n">
-        <v>0.7300255741592796</v>
+        <v>0.7300255741592802</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.6529547236624332</v>
+        <v>-0.6529547236624326</v>
       </c>
       <c r="U37" t="n">
         <v>-0.2017741061690763</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.01216709290265472</v>
+        <v>-0.0121670929026545</v>
       </c>
       <c r="W37" t="n">
         <v>0.01088257872770715</v>
@@ -3839,7 +3839,7 @@
         <v>1.986187875780157</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3648638281031875</v>
+        <v>0.3648638281031877</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         <v>1.410302569216248</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5386876470026671</v>
+        <v>0.5386876470026674</v>
       </c>
       <c r="L44" t="n">
         <v>-0.6658545503552407</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.356822089763472</v>
+        <v>-0.3568220897634722</v>
       </c>
       <c r="N44" t="n">
         <v>0.9341723589663894</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.3769835854750666</v>
+        <v>0.3769835854750665</v>
       </c>
       <c r="Q44" t="n">
         <v>0.1439949164462267</v>
@@ -3889,7 +3889,7 @@
         <v>0.8547288298280291</v>
       </c>
       <c r="T44" t="n">
-        <v>0.3264773618197983</v>
+        <v>0.3264773618197984</v>
       </c>
       <c r="U44" t="n">
         <v>-0.4035482123365095</v>
@@ -3898,7 +3898,7 @@
         <v>-0.01424548049713392</v>
       </c>
       <c r="W44" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="X44" t="n">
         <v>0.006725803538941921</v>
@@ -4151,7 +4151,7 @@
         <v>2.282275391172031</v>
       </c>
       <c r="D48" t="n">
-        <v>1.30113532876273</v>
+        <v>1.301135328762731</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>0.28</v>
       </c>
       <c r="J48" t="n">
-        <v>0.3329272751789759</v>
+        <v>0.3329272751789756</v>
       </c>
       <c r="K48" t="n">
         <v>1.204542197362812</v>
@@ -4180,40 +4180,40 @@
         <v>-1.077375294043014</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.9638612634666792</v>
+        <v>-0.9638612634666793</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2664047011379806</v>
+        <v>0.2664047011379804</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1739502080139231</v>
+        <v>0.1739502080139229</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.6293577649358086</v>
+        <v>0.6293577649358088</v>
       </c>
       <c r="R48" t="n">
-        <v>0.7573969427235077</v>
+        <v>0.7573969427235078</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2017741061690763</v>
+        <v>0.2017741061690762</v>
       </c>
       <c r="T48" t="n">
-        <v>0.7300255741592802</v>
+        <v>0.7300255741592803</v>
       </c>
       <c r="U48" t="n">
         <v>-0.6529547236624326</v>
       </c>
       <c r="V48" t="n">
-        <v>-0.003362901769484616</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="W48" t="n">
         <v>-0.01216709290265472</v>
       </c>
       <c r="X48" t="n">
-        <v>0.01088257872770737</v>
+        <v>0.01088257872770715</v>
       </c>
     </row>
     <row r="49">
@@ -4249,7 +4249,7 @@
         <v>0.28</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3329272751789755</v>
+        <v>-0.3329272751789757</v>
       </c>
       <c r="K49" t="n">
         <v>1.204542197362812</v>
@@ -4258,16 +4258,16 @@
         <v>-1.077375294043014</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.9638612634666793</v>
+        <v>-0.9638612634666792</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.2664047011379803</v>
+        <v>-0.2664047011379805</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.1739502080139229</v>
+        <v>-0.1739502080139231</v>
       </c>
       <c r="Q49" t="n">
         <v>0.6293577649358088</v>
@@ -4276,22 +4276,22 @@
         <v>0.7573969427235077</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.201774106169076</v>
+        <v>-0.2017741061690762</v>
       </c>
       <c r="T49" t="n">
-        <v>0.7300255741592803</v>
+        <v>0.7300255741592802</v>
       </c>
       <c r="U49" t="n">
         <v>-0.6529547236624326</v>
       </c>
       <c r="V49" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.003362901769484616</v>
       </c>
       <c r="W49" t="n">
         <v>-0.01216709290265472</v>
       </c>
       <c r="X49" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.01088257872770737</v>
       </c>
     </row>
     <row r="50">
@@ -4463,7 +4463,7 @@
         <v>2.389155697540901</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2997085997685378</v>
+        <v>0.299708599768538</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4486,13 +4486,13 @@
         <v>1.077375294043014</v>
       </c>
       <c r="K52" t="n">
-        <v>0.3329272751789756</v>
+        <v>0.3329272751789758</v>
       </c>
       <c r="L52" t="n">
         <v>-1.204542197362812</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2952418088443086</v>
+        <v>-0.2952418088443087</v>
       </c>
       <c r="N52" t="n">
         <v>0.9554225632202438</v>
@@ -4501,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.6974829052795894</v>
+        <v>0.6974829052795893</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.2155340710173907</v>
+        <v>0.2155340710173909</v>
       </c>
       <c r="R52" t="n">
         <v>0.6834198278316292</v>
@@ -4513,7 +4513,7 @@
         <v>0.6529547236624329</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2017741061690762</v>
+        <v>0.2017741061690763</v>
       </c>
       <c r="U52" t="n">
         <v>-0.7300255741592799</v>
@@ -4775,7 +4775,7 @@
         <v>2.595824530850536</v>
       </c>
       <c r="D56" t="n">
-        <v>0.8905813499290538</v>
+        <v>0.8905813499290539</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>-1.410302569216248</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.7774375248306198</v>
+        <v>-0.7774375248306199</v>
       </c>
       <c r="N56" t="n">
         <v>0.6289601696333715</v>
@@ -4816,13 +4816,13 @@
         <v>0.5375903897991703</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.6644982658628749</v>
+        <v>0.664498265862875</v>
       </c>
       <c r="R56" t="n">
         <v>0.5190747802203535</v>
       </c>
       <c r="S56" t="n">
-        <v>0.3264773618197986</v>
+        <v>0.3264773618197985</v>
       </c>
       <c r="T56" t="n">
         <v>0.4035482123365096</v>
